--- a/data/Enrollment_2026-07-28.xlsx
+++ b/data/Enrollment_2026-07-28.xlsx
@@ -596,7 +596,7 @@
         <v>2</v>
       </c>
       <c r="G3" s="3">
-        <f t="shared" ref="G3:G9" si="0">SUM(E3:F3)</f>
+        <f t="shared" ref="G3:G7" si="0">SUM(E3:F3)</f>
         <v>7</v>
       </c>
       <c r="I3" s="3">
